--- a/data/data_app.xlsx
+++ b/data/data_app.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jean-\Documents\Stage de Seconde (2)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E7A9B3BA-5968-4A50-A241-5C28A7D1F7C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{997DD8F6-2FEC-4D90-B516-9C9D89A138E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{BA163A98-20A6-4176-B14F-8962F2DE981B}"/>
+    <workbookView xWindow="3405" yWindow="2805" windowWidth="15375" windowHeight="7785" activeTab="1" xr2:uid="{BA163A98-20A6-4176-B14F-8962F2DE981B}"/>
   </bookViews>
   <sheets>
     <sheet name="t_niveau" sheetId="1" r:id="rId1"/>
-    <sheet name="t_parent" sheetId="2" r:id="rId2"/>
-    <sheet name="t_enfant" sheetId="3" r:id="rId3"/>
+    <sheet name="t_cours" sheetId="4" r:id="rId2"/>
+    <sheet name="t_parent" sheetId="2" r:id="rId3"/>
+    <sheet name="t_enfant" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="41">
   <si>
     <t>Niveau 1</t>
   </si>
@@ -132,12 +133,33 @@
   </si>
   <si>
     <t>Luc</t>
+  </si>
+  <si>
+    <t>cours_id</t>
+  </si>
+  <si>
+    <t>cours_date</t>
+  </si>
+  <si>
+    <t>cours_heure_debut</t>
+  </si>
+  <si>
+    <t>cours_heure_fin</t>
+  </si>
+  <si>
+    <t>cours_niveau</t>
+  </si>
+  <si>
+    <t>cours_capacite</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -173,11 +195,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -619,6 +643,143 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3087F385-D869-494B-B5C0-59943C68AC9B}">
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2">
+        <v>46087</v>
+      </c>
+      <c r="C2" s="3">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="D2" s="3">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2">
+        <v>46088</v>
+      </c>
+      <c r="C3" s="3">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="D3" s="3">
+        <v>0.375</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2">
+        <v>46089</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0.375</v>
+      </c>
+      <c r="D4" s="3">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="E4">
+        <v>3</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2">
+        <v>46090</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="D5" s="3">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="E5">
+        <v>11</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2">
+        <v>46091</v>
+      </c>
+      <c r="C6" s="3">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D6" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E6">
+        <v>6</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E0E413A-252C-4F2C-805F-78605CA58DBB}">
   <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -687,7 +848,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7ED6F87D-DF3D-4360-80AA-2F637F1B511A}">
   <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
